--- a/APPD_LAB_DETAILS.xlsx
+++ b/APPD_LAB_DETAILS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/12ea3443da50b1a8/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{3569AA14-81C5-4241-925A-51DDD0E4661A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F78626B-CB9D-4B74-88BC-DDBD2008385F}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{3569AA14-81C5-4241-925A-51DDD0E4661A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A415937C-0596-4AC3-B5EF-7F5C4DBE79DC}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9ADF650-3201-4E59-8732-722D9C83084B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
   <si>
     <t>Name</t>
   </si>
@@ -241,6 +241,24 @@
   </si>
   <si>
     <t>2)WO5T-dL314)*5Wla%EHkPjRZ44!7P3</t>
+  </si>
+  <si>
+    <t>IP Address ---6</t>
+  </si>
+  <si>
+    <t>13.233.250.219</t>
+  </si>
+  <si>
+    <t>65.2.172.246</t>
+  </si>
+  <si>
+    <t>13.127.181.19</t>
+  </si>
+  <si>
+    <t>3.110.131.67</t>
+  </si>
+  <si>
+    <t>35.154.134.117</t>
   </si>
 </sst>
 </file>
@@ -633,26 +651,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD0A8AD-A451-44A9-AFF6-F392D5E3F55B}">
-  <dimension ref="A2:O7"/>
+  <dimension ref="A2:P7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="26.6640625" customWidth="1"/>
-    <col min="8" max="8" width="20.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="37.33203125" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" customWidth="1"/>
-    <col min="11" max="11" width="16.77734375" customWidth="1"/>
-    <col min="12" max="12" width="15.88671875" customWidth="1"/>
-    <col min="13" max="13" width="17.44140625" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="10" max="12" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -698,8 +715,11 @@
       <c r="O2" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="P2" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -745,8 +765,11 @@
       <c r="O3" s="5" t="s">
         <v>60</v>
       </c>
+      <c r="P3" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -792,8 +815,11 @@
       <c r="O4" s="5" t="s">
         <v>68</v>
       </c>
+      <c r="P4" s="5" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -839,8 +865,11 @@
       <c r="O5" s="5" t="s">
         <v>67</v>
       </c>
+      <c r="P5" s="5" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -886,8 +915,11 @@
       <c r="O6" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="P6" s="5" t="s">
+        <v>73</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -932,6 +964,9 @@
       </c>
       <c r="O7" s="5" t="s">
         <v>65</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
